--- a/data/guru.xlsx
+++ b/data/guru.xlsx
@@ -1,34 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+  <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Guru" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guru" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1" calcId="124519"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24" count="24">
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>NIP</t>
+  </si>
+  <si>
+    <t>Jabatan</t>
+  </si>
+  <si>
+    <t>No HP</t>
+  </si>
+  <si>
+    <t>Ahmad Junaedi Fatah, S.Pd.SD</t>
+  </si>
+  <si>
+    <t>198001012005011001</t>
+  </si>
+  <si>
+    <t>Kepala Sekolah</t>
+  </si>
+  <si>
+    <t>081234567890</t>
+  </si>
+  <si>
+    <t>Marsiah, S.Pd</t>
+  </si>
+  <si>
+    <t>Eka Priawan, S.Pd.</t>
+  </si>
+  <si>
+    <t>Puji Lestari, S.Pd.</t>
+  </si>
+  <si>
+    <t>Andi Setyowati, S.Pd.</t>
+  </si>
+  <si>
+    <t>Desti Nur Islami, S.Pd.</t>
+  </si>
+  <si>
+    <t>Nani Hidayani, S.Pd.</t>
+  </si>
+  <si>
+    <t>Kristiana Dewi, S.A.P.</t>
+  </si>
+  <si>
+    <t>Rizal Agustianto (PJOK)</t>
+  </si>
+  <si>
+    <t>Zaenal wkwkwk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rizal Agustianto </t>
+  </si>
+  <si>
+    <t>Guru Kelas</t>
+  </si>
+  <si>
+    <t>Guru Agama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenaga Administrasi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PJOK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">adalah pokoknya </t>
+  </si>
+  <si>
+    <t>Nani Hidayani, S.Pd.I.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -44,15 +118,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -341,7 +420,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
+            <a:lightRig dir="t" rig="threePt">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -408,59 +487,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="26.214844" style="0"/>
+    <col min="2" max="2" customWidth="1" width="17.066406" style="0"/>
+    <col min="3" max="3" customWidth="1" width="16.496094" style="0"/>
+    <col min="4" max="4" customWidth="1" width="11.644531" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nama</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>NIP</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Jabatan</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>No HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ahmad Junaedi Fatah, S.Pd.SD</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>198001012005011001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Kepala Sekolah</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>081234567890</t>
-        </is>
+    <row r="1" spans="8:8" ht="17.0">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="8:8" ht="17.0">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="8:8" ht="17.0">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="8:8" ht="17.0">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8" ht="17.0">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8" ht="17.0">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8" ht="17.0">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8" ht="17.0">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8" ht="17.0">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8" ht="17.0">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8" ht="17.0">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
 </worksheet>
 </file>